--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -607,7 +607,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,28 +615,48 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>423993</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:09.236Z</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2024-05-05T07:28:48Z</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -646,12 +666,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12jTPoyQzBxOhbpog6uRie5gwB1IG-9O-/view</t>
+          <t>https://drive.google.com/file/d/12jTPoyQzBxOhbpog6uRie5gwB1IG-9O-/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,7 +835,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -823,28 +843,48 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>209329</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:10.014Z</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2024-12-19T10:52:34Z</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1148</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -854,12 +894,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UhYnUWV8PCpkc0Tmw6cnSKqT12zerfNt/view</t>
+          <t>https://drive.google.com/file/d/1UhYnUWV8PCpkc0Tmw6cnSKqT12zerfNt/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1003,7 +1043,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+          <t>اقرار من الوالدة عاتقة توكيل الثعلي في الدعوى 42824717 ضد اسامة زيني ـ 04-03-1445.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1011,43 +1051,63 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>234603</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:17:47.264Z</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-02-14T11:19:18Z</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>وكالة</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S-JsbhtGsPL0ebxRRRzXIwqWQO6jU_du/view</t>
+          <t>https://drive.google.com/file/d/1S-JsbhtGsPL0ebxRRRzXIwqWQO6jU_du/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1135,7 +1195,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1143,43 +1203,63 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>181781</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:17:47.143Z</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2018-07-05T08:30:53Z</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5736</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Rxq8Tf2lFge44D895x_YlVhSKhhT6kAH/view</t>
+          <t>https://drive.google.com/file/d/1Rxq8Tf2lFge44D895x_YlVhSKhhT6kAH/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1379,7 +1459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى المقيدة برقم (42824717) وقضية أرض التنس.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2359,7 +2439,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2367,43 +2447,63 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.wordprocessingml.document</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30282</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:05.695Z</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-10-16T04:36:40Z</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>14643</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m8dl8PmAPDFJTVs25MmTH7SZAf5QFV_Y/view</t>
+          <t>https://drive.google.com/file/d/1m8dl8PmAPDFJTVs25MmTH7SZAf5QFV_Y/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2735,7 +2835,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2743,28 +2843,48 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>79283</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:11.066Z</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2024-05-22T04:38:06Z</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1792</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2774,12 +2894,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TnwCWqP5WHA2ZXwy0GFbsx9DY9JuC_Io/view</t>
+          <t>https://drive.google.com/file/d/1TnwCWqP5WHA2ZXwy0GFbsx9DY9JuC_Io/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2943,7 +3063,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+          <t>تقييم العيوطي للشركات.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2951,43 +3071,63 @@
           <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4260367</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:20:32.858Z</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2024-03-13T07:40:32Z</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14UdnHAbZOv9SZXnO3mMrkPePnXfEQFu9/view</t>
+          <t>https://drive.google.com/file/d/14UdnHAbZOv9SZXnO3mMrkPePnXfEQFu9/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3167,7 +3307,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3175,28 +3315,48 @@
           <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>153327</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:17:48.539Z</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2024-07-15T08:17:17Z</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1838</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3206,12 +3366,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TzsNmsfPLd1D-ds7zyE_xKKPfZtMZNNJ/view</t>
+          <t>https://drive.google.com/file/d/1TzsNmsfPLd1D-ds7zyE_xKKPfZtMZNNJ/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3843,7 +4003,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3851,28 +4011,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>797889</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:05.972Z</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-02-22T07:37:51Z</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1915</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3882,12 +4062,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JSlPkKqEnnaJVucKZYiQ19CX_HxKw3My/view</t>
+          <t>https://drive.google.com/file/d/1JSlPkKqEnnaJVucKZYiQ19CX_HxKw3My/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4011,7 +4191,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4019,28 +4199,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>203686</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:05.911Z</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-02-17T10:33:10Z</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>3717</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4050,12 +4250,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TOjPciWFiww2D2rsm57qGXkLL-QlSToP/view</t>
+          <t>https://drive.google.com/file/d/1TOjPciWFiww2D2rsm57qGXkLL-QlSToP/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -4459,7 +4659,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>طلب النقض الأخير ـ 07-10-1447</t>
+          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4467,11 +4667,31 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>182371</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:32:28.391Z</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:33:51Z</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>لا</t>
@@ -4503,7 +4723,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JsER2PVyIe5q3zXv3zAURxA-JkYXe3qs/view</t>
+          <t>https://drive.google.com/file/d/1JsER2PVyIe5q3zXv3zAURxA-JkYXe3qs/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -4627,7 +4847,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4635,28 +4855,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>4453030</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:19:10.030Z</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2024-09-18T11:34:39Z</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2481</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4666,12 +4906,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YZch0mcY3_pGTtMtaN5a0cqqNAUqO7Q2/view</t>
+          <t>https://drive.google.com/file/d/1YZch0mcY3_pGTtMtaN5a0cqqNAUqO7Q2/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -4851,7 +5091,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,43 +5099,63 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>315646</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:07.228Z</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2024-03-02T18:37:10Z</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1965</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z3cWsKqImdcuh0EpjGqR3rM2xw5aHgsT/view</t>
+          <t>https://drive.google.com/file/d/1z3cWsKqImdcuh0EpjGqR3rM2xw5aHgsT/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -4907,7 +5167,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4915,28 +5175,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4900930</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:19:24.066Z</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2024-08-27T16:51:12Z</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>3058</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4946,12 +5226,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HVbLJm6BQ4picvDOwVgvqMGPcBQNlvdZ/view</t>
+          <t>https://drive.google.com/file/d/1HVbLJm6BQ4picvDOwVgvqMGPcBQNlvdZ/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -4963,7 +5243,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4971,28 +5251,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.wordprocessingml.document</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>25510</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:07.249Z</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-12-30T11:46:36Z</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>9995</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5002,12 +5302,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1q_HFBphb1eUvasmZs2w5IXBcC--BuaHL/view</t>
+          <t>https://drive.google.com/file/d/1q_HFBphb1eUvasmZs2w5IXBcC--BuaHL/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5151,7 +5451,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5159,43 +5459,63 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>5200379</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:19:27.123Z</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2024-08-27T17:00:56Z</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1x6jb5RIYxxQpbQqNsTYhpwnGf4g5GoGJ/view</t>
+          <t>https://drive.google.com/file/d/1x6jb5RIYxxQpbQqNsTYhpwnGf4g5GoGJ/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -5375,7 +5695,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>مذكرة جوابية ـ 16-08-1445</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5383,43 +5703,63 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>386714</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:07.515Z</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2024-03-02T18:31:50Z</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16KPeg8Q57KIeFlKlgKFIQpZfj3EhMvZT/view</t>
+          <t>https://drive.google.com/file/d/16KPeg8Q57KIeFlKlgKFIQpZfj3EhMvZT/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -5487,7 +5827,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5495,28 +5835,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>4491152</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:19:35.977Z</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2024-02-25T08:52:33Z</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>3310</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5526,12 +5886,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mYbMRrqkZYca6OZBZ1x8QW09puKH645z/view</t>
+          <t>https://drive.google.com/file/d/1mYbMRrqkZYca6OZBZ1x8QW09puKH645z/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6275,7 +6635,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6283,28 +6643,48 @@
           <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>33206</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:08.563Z</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2021-12-01T05:03:21Z</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1962</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6314,12 +6694,12 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UgLzFge8qYnoXnkMh7EWqMVaEMajlkC4/view</t>
+          <t>https://drive.google.com/file/d/1UgLzFge8qYnoXnkMh7EWqMVaEMajlkC4/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -7679,7 +8059,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>التماس في الدعوى ـ نسخة ثانية</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7687,28 +8067,48 @@
           <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.wordprocessingml.document</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>20848</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:12.533Z</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2024-01-13T14:34:30Z</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>4503</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7718,12 +8118,12 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U-DWBW5EmqXWmY6UP4zza2EGeLuHN8Io/view</t>
+          <t>https://drive.google.com/file/d/1U-DWBW5EmqXWmY6UP4zza2EGeLuHN8Io/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -7791,7 +8191,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+          <t>جزء من مسحوبات مصروفات الشيخ احمد زيني رحمه الله.pdf</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7799,28 +8199,48 @@
           <t>ز. مرفقات مذكرة الالتماس ـ أُرفقت 06-08-1445 (5 ملفات)</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>872200</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:10.336Z</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2024-03-13T07:43:14Z</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7830,12 +8250,12 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16Ntp_ehFpXV_QiX0uU0f2iPoQ87ivLxs/view</t>
+          <t>https://drive.google.com/file/d/16Ntp_ehFpXV_QiX0uU0f2iPoQ87ivLxs/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -7903,7 +8323,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>جزء من مصروفات فيلا الوادي</t>
+          <t>جزء من مصروفات فيلا الوادي.pdf</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7911,28 +8331,48 @@
           <t>ز. مرفقات مذكرة الالتماس ـ أُرفقت 06-08-1445 (5 ملفات)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1395769</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:20:38.095Z</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2024-03-13T07:44:21Z</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7942,12 +8382,12 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V9aM64Q773mHIW0cRKQMqfAc8aIokWGs/view</t>
+          <t>https://drive.google.com/file/d/1V9aM64Q773mHIW0cRKQMqfAc8aIokWGs/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -8911,7 +9351,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>مصاريف المزرعة (Excel)</t>
+          <t>مصاريف مزرعة الشيخ أحمد زيني بالوادي (1).xlsx</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8919,43 +9359,63 @@
           <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.spreadsheetml.sheet</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>27174</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:12.656Z</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2024-09-09T06:40:56Z</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>49851</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>مستند مالي</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SNh5aI1IhHNBS5S2wg5b6AAb_osujWDK/view</t>
+          <t>https://drive.google.com/file/d/1SNh5aI1IhHNBS5S2wg5b6AAb_osujWDK/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -9191,7 +9651,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>مصاريف فيلا الوادي (Excel)</t>
+          <t>excelمصاريف فيلا الشيخ أحمد زيني بالوادي.xlsx</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9199,43 +9659,63 @@
           <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.spreadsheetml.sheet</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>15528</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:12.685Z</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2024-09-09T06:38:30Z</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>15527</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>مستند مالي</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lXSmR7XFizz6MJQKzmkoCz1BmFc0kNCB/view</t>
+          <t>https://drive.google.com/file/d/1lXSmR7XFizz6MJQKzmkoCz1BmFc0kNCB/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -9415,7 +9895,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>موجز الشكوى للمجلس الأعلى</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9423,28 +9903,48 @@
           <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1176063</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:40.660Z</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2024-10-29T10:46:28Z</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>2987</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9454,12 +9954,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Lsz2NG_acc1g_BL7VDEJy9BD6ZGscELg/view</t>
+          <t>https://drive.google.com/file/d/1Lsz2NG_acc1g_BL7VDEJy9BD6ZGscELg/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -9979,7 +10479,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9987,28 +10487,48 @@
           <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.wordprocessingml.document</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>50693</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:10.940Z</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2023-11-21T08:29:13Z</t>
+        </is>
+      </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>8173</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -10018,12 +10538,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/180gGxs0eNvNmvOAkILRmwFNTqkaI4tiP/view</t>
+          <t>https://drive.google.com/file/d/180gGxs0eNvNmvOAkILRmwFNTqkaI4tiP/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -10035,7 +10555,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10043,28 +10563,48 @@
           <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>5407202</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:21:05.805Z</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2024-05-21T19:37:27Z</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>137510</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -10074,12 +10614,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1R77OSQfzc29NIkq84RTxHSDhg60gFwcr/view</t>
+          <t>https://drive.google.com/file/d/1R77OSQfzc29NIkq84RTxHSDhg60gFwcr/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -10727,7 +11267,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10735,28 +11275,48 @@
           <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>4193072</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:27.655Z</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2024-05-21T19:42:37Z</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
-        <v>0</v>
+        <v>134309</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -10766,12 +11326,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U3bYf5KLk19hdBWRa1WYwbwhAMJvOY7m/view</t>
+          <t>https://drive.google.com/file/d/1U3bYf5KLk19hdBWRa1WYwbwhAMJvOY7m/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -10895,7 +11455,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى (صورة)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10903,28 +11463,48 @@
           <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>image/jpeg</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>73862</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:03.573Z</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2024-05-22T04:34:22Z</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -10934,12 +11514,12 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1piRGnIrlALLMuPsl2RDETl-GPkM-7Ol4/view</t>
+          <t>https://drive.google.com/file/d/1piRGnIrlALLMuPsl2RDETl-GPkM-7Ol4/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -11063,7 +11643,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11071,28 +11651,48 @@
           <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3522945</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:34.007Z</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2024-10-29T13:34:40Z</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>135125</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11102,12 +11702,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qR8qS40taRQojtf7_fNKiVec3pIdPBML/view</t>
+          <t>https://drive.google.com/file/d/1qR8qS40taRQojtf7_fNKiVec3pIdPBML/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -11679,7 +12279,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11687,43 +12287,63 @@
           <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>77708</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:05.243Z</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2024-05-26T06:48:14Z</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>1470</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LiTuA3nEHgYZR98cBPGolr9SFr0Hf5Ho/view</t>
+          <t>https://drive.google.com/file/d/1LiTuA3nEHgYZR98cBPGolr9SFr0Hf5Ho/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -12015,7 +12635,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12023,28 +12643,48 @@
           <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>application/vnd.openxmlformats-officedocument.wordprocessingml.document</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>14214</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:18:05.651Z</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2025-07-17T12:07:21Z</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
-        <v>0</v>
+        <v>3594</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -12054,12 +12694,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TXwIiZOBvKF-HbFxAhXw1rK0-p1UmXVy/view</t>
+          <t>https://drive.google.com/file/d/1TXwIiZOBvKF-HbFxAhXw1rK0-p1UmXVy/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -12071,7 +12711,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>مذكرة الالتماس ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12079,28 +12719,48 @@
           <t>س. مذكرة التماس المحامي الشهري ـ 13-07-1445 (ملف واحد)</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>application/pdf</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>4900930</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-04-07T11:20:14.501Z</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2024-08-27T16:51:12Z</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>1482</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>visual/OCR-reversed</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -12110,12 +12770,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1drvTbOtOVH14FiHvGQIOSguiTg3wJiPI/view</t>
+          <t>https://drive.google.com/file/d/1drvTbOtOVH14FiHvGQIOSguiTg3wJiPI/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -8750,31 +8750,31 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>90377</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8806,31 +8806,31 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>59438</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8862,31 +8862,31 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>70978</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8918,31 +8918,31 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>43086</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -9142,31 +9142,31 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>29527</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -9198,31 +9198,31 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>20062</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -9254,31 +9254,31 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>20169</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -9310,31 +9310,31 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>13421</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -9554,31 +9554,31 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>31221</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>تقرير خبرة</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9610,21 +9610,21 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>7630</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9798,21 +9798,21 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11170,31 +11170,31 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -4694,21 +4694,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>visual/OCR-reversed</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>129684</v>
+        <v>130737</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>129684</v>
+        <v>40727</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>12265</v>
+        <v>10238</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>3717</v>
+        <v>11451</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
-        <v>5778</v>
+        <v>4724</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
-        <v>5384</v>
+        <v>4657</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>مستند مالي</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
-        <v>5332</v>
+        <v>4627</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>5247</v>
+        <v>4602</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
-        <v>5240</v>
+        <v>4611</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>5179</v>
+        <v>4461</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>5406</v>
+        <v>4631</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
-        <v>5304</v>
+        <v>4600</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>5523</v>
+        <v>4783</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>5475</v>
+        <v>4799</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>8628</v>
+        <v>7727</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>8584</v>
+        <v>7399</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>12717</v>
+        <v>11672</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>36236</v>
+        <v>31989</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
-        <v>129684</v>
+        <v>130408</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>906</v>
+        <v>33174</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>835</v>
+        <v>29914</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
-        <v>10451</v>
+        <v>10328</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
-        <v>1923</v>
+        <v>7297</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>2553</v>
+        <v>11401</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>1148</v>
+        <v>13683</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>1965</v>
+        <v>9238</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>2022</v>
+        <v>40727</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>

--- a/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
+++ b/zaini_case_audit_output/outputs/excel/01_full_file_inventory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12784,6 +12784,168 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="n">
+        <v>211279</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>69191</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="n">
+        <v>364835</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="n">
+        <v>19655</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="n">
+        <v>286216</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="n">
+        <v>4</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>logical</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
